--- a/artfynd/A 7807-2026 artfynd.xlsx
+++ b/artfynd/A 7807-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103812537</v>
+        <v>103812539</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612259.2039341739</v>
+        <v>612259</v>
       </c>
       <c r="R2" t="n">
-        <v>7177494.954725783</v>
+        <v>7177495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103812539</v>
+        <v>103812537</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612259.2039341739</v>
+        <v>612259</v>
       </c>
       <c r="R3" t="n">
-        <v>7177494.954725783</v>
+        <v>7177495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-08-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,19 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103814721</v>
+        <v>103812541</v>
       </c>
       <c r="B4" t="n">
-        <v>57073</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -948,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612066.4194982077</v>
+        <v>612067</v>
       </c>
       <c r="R4" t="n">
-        <v>7177226.188534333</v>
+        <v>7177226</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +946,9 @@
           <t>2022-08-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
